--- a/marketing_report/outputs/Posgrados/tabla_utm_campaigns.xlsx
+++ b/marketing_report/outputs/Posgrados/tabla_utm_campaigns.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="23">
   <si>
     <t>UtmCampaign</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>21772187688</t>
+  </si>
+  <si>
+    <t>23220287690</t>
   </si>
   <si>
     <t>googleads</t>
@@ -437,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -471,10 +474,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -497,10 +500,10 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -523,10 +526,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -549,10 +552,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -575,10 +578,10 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -601,10 +604,10 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -627,10 +630,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -653,10 +656,10 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -679,10 +682,10 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -705,24 +708,50 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
         <v>100</v>
       </c>
     </row>

--- a/marketing_report/outputs/Posgrados/tabla_utm_campaigns.xlsx
+++ b/marketing_report/outputs/Posgrados/tabla_utm_campaigns.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
   <si>
     <t>UtmCampaign</t>
   </si>
@@ -40,15 +40,15 @@
     <t>Tasa_Conversion_%</t>
   </si>
   <si>
+    <t>120235998797960048</t>
+  </si>
+  <si>
+    <t>14875022827</t>
+  </si>
+  <si>
     <t>14876203835</t>
   </si>
   <si>
-    <t>120235998797960048</t>
-  </si>
-  <si>
-    <t>14875022827</t>
-  </si>
-  <si>
     <t>14893252513</t>
   </si>
   <si>
@@ -64,25 +64,22 @@
     <t>15767139553</t>
   </si>
   <si>
-    <t>21676468921</t>
-  </si>
-  <si>
     <t>21772187688</t>
   </si>
   <si>
     <t>23220287690</t>
   </si>
   <si>
+    <t>ig</t>
+  </si>
+  <si>
     <t>googleads</t>
   </si>
   <si>
-    <t>ig</t>
+    <t>paid</t>
   </si>
   <si>
     <t>leads</t>
-  </si>
-  <si>
-    <t>paid</t>
   </si>
 </sst>
 </file>
@@ -440,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -474,22 +471,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>100</v>
@@ -500,10 +497,10 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -726,32 +723,6 @@
         <v>1</v>
       </c>
       <c r="H11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
         <v>100</v>
       </c>
     </row>
